--- a/literature-review/snowballing/snowballing_topic1.xlsx
+++ b/literature-review/snowballing/snowballing_topic1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DBAB47-133B-41A1-B690-95AF32D93454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADB2881-65A3-416D-94A0-36EC6D12BC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3456" yWindow="2784" windowWidth="26556" windowHeight="14496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="30960" windowHeight="14244" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="44">
   <si>
     <t>Inclusion Criteria</t>
   </si>
@@ -90,21 +90,9 @@
     <t>Backward Snowballing Results</t>
   </si>
   <si>
-    <t>Efficient and Robust Automated Machine Learning</t>
-  </si>
-  <si>
-    <t>Matthias Feurer, Aaron Klein, Katharina Eggensperger, Jost Tobias Springenberg, Manuel Blum, Frank Hutter</t>
-  </si>
-  <si>
     <t>ARTICLE</t>
   </si>
   <si>
-    <t>Advances in neural information processing systems</t>
-  </si>
-  <si>
-    <t>https://proceedings.neurips.cc/paper_files/paper/2015/file/11d0e6287202fced83f79975ec59a3a6-Paper.pdf</t>
-  </si>
-  <si>
     <t>✅</t>
   </si>
   <si>
@@ -163,6 +151,12 @@
   </si>
   <si>
     <t>Especially relevant</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/stamp/stamp.jsp?tp=&amp;arnumber=10283095</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0167739X24004631/pdfft?md5=523bb92402be8f64ea38e47ead45e895&amp;pid=1-s2.0-S0167739X24004631-main.pdf</t>
   </si>
 </sst>
 </file>
@@ -203,7 +197,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor rgb="FFC4D79B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -260,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -268,19 +262,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC4D79B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -555,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" customWidth="1"/>
@@ -633,267 +633,269 @@
       <c r="Q3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="11"/>
-    </row>
-    <row r="4" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
+      <c r="R3" s="7"/>
+    </row>
+    <row r="4" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="8">
+        <v>2023</v>
+      </c>
+      <c r="E4" s="8">
+        <v>5</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="G4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="7">
-        <v>2015</v>
-      </c>
-      <c r="E4" s="7">
-        <v>2894</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="9"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
       <c r="Q4" s="10"/>
-    </row>
-    <row r="5" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+      <c r="R4" s="8"/>
+    </row>
+    <row r="8" spans="1:18" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B8" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="R10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>0</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D11" s="8">
         <v>2023</v>
       </c>
-      <c r="E5" s="7">
-        <v>5</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="8"/>
+    </row>
+    <row r="12" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>1</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="10"/>
-      <c r="Q5" s="10"/>
-    </row>
-    <row r="9" spans="1:18" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B9" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="I10" s="1" t="s">
+      <c r="C12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="8">
+        <v>2024</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="8"/>
+    </row>
+    <row r="13" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>2</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="8">
+        <v>2023</v>
+      </c>
+      <c r="E13" s="8">
         <v>0</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="F13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="8"/>
+    </row>
+    <row r="14" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
         <v>3</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="R11" s="11"/>
-    </row>
-    <row r="12" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
+      <c r="B14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="8">
+        <v>2024</v>
+      </c>
+      <c r="E14" s="8">
         <v>0</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="7">
-        <v>2023</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="9"/>
-      <c r="Q12" s="10"/>
-    </row>
-    <row r="13" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
-        <v>1</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="7">
-        <v>2024</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="10"/>
-      <c r="Q13" s="10"/>
-    </row>
-    <row r="14" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
-        <v>2</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="7">
-        <v>2023</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="F14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="10"/>
-      <c r="Q14" s="10"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
-        <v>3</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="7">
-        <v>2024</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="R15" s="7"/>
+      <c r="R14" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
